--- a/inferences/jesuita-entrada-Coimbra-cargos_tarefas.xlsx
+++ b/inferences/jesuita-entrada-Coimbra-cargos_tarefas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cargos_tarefas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cargos_tarefas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2383,17 +2383,17 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Provincial do Japão e da China</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2415,17 +2415,17 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Provincial do Japão e da China</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2767,17 +2767,17 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Provincial do Japão e da China</t>
+          <t>Visitador das províncias de Goa e do Malabar</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Visitador das províncias de Goa e do Malabar</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2831,17 +2831,17 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Provincial do Japão e da China</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4335,17 +4335,17 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-gouvea</t>
+          <t>deh-matias-da-maia</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>António de Gouveia</t>
+          <t>Matias da Maia</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Visitador</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Reitor do Colégio de Macau</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4399,17 +4399,17 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>deh-matias-da-maia</t>
+          <t>deh-antonio-de-gouvea</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Matias da Maia</t>
+          <t>António de Gouveia</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Reitor do Colégio de Macau</t>
+          <t>Visitador</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4751,17 +4751,17 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>deh-leonardo-teixeira</t>
+          <t>deh-antonio-da-silva</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Leonardo Teixeira</t>
+          <t>António da Silva</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Superior</t>
+          <t>Reitor de Nanquim</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4783,17 +4783,17 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-da-silva</t>
+          <t>deh-leonardo-teixeira</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>António da Silva</t>
+          <t>Leonardo Teixeira</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Reitor de Nanquim</t>
+          <t>Superior</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>deh-miguel-do-amaral</t>
+          <t>deh-francisco-pinto-i</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Miguel do Amaral</t>
+          <t>Francisco Pinto</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5263,12 +5263,12 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pinto-i</t>
+          <t>deh-miguel-do-amaral</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Francisco Pinto</t>
+          <t>Miguel do Amaral</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5743,17 +5743,17 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>deh-miguel-do-amaral</t>
+          <t>deh-francisco-pinto-i</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Miguel do Amaral</t>
+          <t>Francisco Pinto</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Procurador da Vice-província da China</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Vice-visitador do Japão</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5807,17 +5807,17 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pinto-i</t>
+          <t>deh-miguel-do-amaral</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Francisco Pinto</t>
+          <t>Miguel do Amaral</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Vice-visitador do Japão</t>
+          <t>Procurador da Vice-província da China</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">

--- a/inferences/jesuita-entrada-Coimbra-cargos_tarefas.xlsx
+++ b/inferences/jesuita-entrada-Coimbra-cargos_tarefas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cargos_tarefas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="cargos_tarefas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:F179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,17 +463,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-furtado</t>
+          <t>deh-francisco-vieira</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Francisco Furtado</t>
+          <t>Francisco Vieira</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Procurador</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-perez</t>
+          <t>deh-francisco-furtado</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Francisco Pérez</t>
+          <t>Francisco Furtado</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Funda uma residência</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -537,17 +537,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Superior das Índias</t>
+          <t>Funda uma residência</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,17 +559,17 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-nunes-barreto</t>
+          <t>deh-francisco-perez</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Belchior Nunes Barreto</t>
+          <t>Francisco Pérez</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vice-provincial das Índias Orientais</t>
+          <t>Superior das Índias</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Resgata cativos portugueses</t>
+          <t>Vice-provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,22 +623,22 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>deh-tiburcio-de-quadros</t>
+          <t>deh-belchior-nunes-barreto</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tibúrcio de Quadros</t>
+          <t>Belchior Nunes Barreto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Provincial da Etiópia</t>
+          <t>Resgata cativos portugueses</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-nunes-barreto</t>
+          <t>deh-tiburcio-de-quadros</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Belchior Nunes Barreto</t>
+          <t>Tibúrcio de Quadros</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Resgata cativos portugueses</t>
+          <t>Provincial da Etiópia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,22 +687,22 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>deh-tiburcio-de-quadros</t>
+          <t>deh-belchior-nunes-barreto</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tibúrcio de Quadros</t>
+          <t>Belchior Nunes Barreto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vice-provincial das Índias Orientais</t>
+          <t>Resgata cativos portugueses</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -719,22 +719,22 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-nunes-barreto</t>
+          <t>deh-tiburcio-de-quadros</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Belchior Nunes Barreto</t>
+          <t>Tibúrcio de Quadros</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Funda a missão de Kwangtung</t>
+          <t>Vice-provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -751,22 +751,22 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>deh-tiburcio-de-quadros</t>
+          <t>deh-belchior-nunes-barreto</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tibúrcio de Quadros</t>
+          <t>Belchior Nunes Barreto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vice-provincial das Índias Orientais</t>
+          <t>Funda a missão de Kwangtung</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Provincial das Índias Orientais</t>
+          <t>Vice-provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Superior da China</t>
+          <t>Provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -847,27 +847,27 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-perez</t>
+          <t>deh-tiburcio-de-quadros</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Francisco Pérez</t>
+          <t>Tibúrcio de Quadros</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Funda a residência jesuíta de Macau</t>
+          <t>Superior da China</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -879,27 +879,27 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-nunes-barreto</t>
+          <t>deh-francisco-perez</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Belchior Nunes Barreto</t>
+          <t>Francisco Pérez</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vice-provincial de Cochim</t>
+          <t>Funda a residência jesuíta de Macau</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -911,17 +911,17 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-perez</t>
+          <t>deh-belchior-nunes-barreto</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Francisco Pérez</t>
+          <t>Belchior Nunes Barreto</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Superior de Macau</t>
+          <t>Vice-provincial de Cochim</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Funda a residência jesuíta de Macau</t>
+          <t>Superior de Macau</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -975,27 +975,27 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-nunes-barreto</t>
+          <t>deh-francisco-perez</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Belchior Nunes Barreto</t>
+          <t>Francisco Pérez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Visitador da Província da Índia</t>
+          <t>Funda a residência jesuíta de Macau</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>deh-goncalo-alvares</t>
+          <t>deh-belchior-nunes-barreto</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gonçalo Álvares</t>
+          <t>Belchior Nunes Barreto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Visitador das Índias e do Japão</t>
+          <t>Visitador da Província da Índia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1039,27 +1039,27 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-miguel-carneiro-leitao</t>
+          <t>deh-goncalo-alvares</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Belchior Miguel Carneiro Leitão</t>
+          <t>Gonçalo Álvares</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Funda o hospital de Macau</t>
+          <t>Visitador das Índias e do Japão</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1071,17 +1071,17 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>deh-goncalo-alvares</t>
+          <t>deh-belchior-miguel-carneiro-leitao</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gonçalo Álvares</t>
+          <t>Belchior Miguel Carneiro Leitão</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manda abrir uma escola elementar</t>
+          <t>Funda o hospital de Macau</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1103,22 +1103,22 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>deh-tiburcio-de-quadros</t>
+          <t>deh-goncalo-alvares</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tibúrcio de Quadros</t>
+          <t>Gonçalo Álvares</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Provincial das Índias Orientais</t>
+          <t>Manda abrir uma escola elementar</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Superior da China</t>
+          <t>Provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1167,17 +1167,17 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>deh-cristovao-da-costa</t>
+          <t>deh-tiburcio-de-quadros</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cristóvão da Costa</t>
+          <t>Tibúrcio de Quadros</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Superior de Macau</t>
+          <t>Superior da China</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1199,17 +1199,17 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>deh-lourenco-mexia</t>
+          <t>deh-cristovao-da-costa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lourenço Mexia</t>
+          <t>Cristóvão da Costa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monitor de Alessandro Valignano</t>
+          <t>Superior de Macau</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Analista das missões da China e do Japão</t>
+          <t>Monitor de Alessandro Valignano</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,17 +1295,17 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>deh-pedro-martins</t>
+          <t>deh-lourenco-mexia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pedro Martins</t>
+          <t>Lourenço Mexia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reitor de Goa</t>
+          <t>Analista das missões da China e do Japão</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Provincial das Índias Orientais</t>
+          <t>Reitor de Goa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>deh-lourenco-mexia</t>
+          <t>deh-pedro-martins</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lourenço Mexia</t>
+          <t>Pedro Martins</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Superior da residência de Macau</t>
+          <t>Provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Analista das missões da China e do Japão</t>
+          <t>Superior da residência de Macau</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1423,17 +1423,17 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>deh-nicolau-pimenta</t>
+          <t>deh-lourenco-mexia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nicolau Pimenta</t>
+          <t>Lourenço Mexia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Visitador das Índias Orientais</t>
+          <t>Analista das missões da China e do Japão</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1519,17 +1519,17 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>deh-lourenco-mexia</t>
+          <t>deh-nicolau-pimenta</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lourenço Mexia</t>
+          <t>Nicolau Pimenta</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Analista das missões da China e do Japão</t>
+          <t>Visitador das Índias Orientais</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1583,27 +1583,27 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>deh-nicolau-pimenta</t>
+          <t>deh-lourenco-mexia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nicolau Pimenta</t>
+          <t>Lourenço Mexia</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Promotor da missão em África</t>
+          <t>Analista das missões da China e do Japão</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Visitador das Índias Orientais</t>
+          <t>Promotor da missão em África</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1647,17 +1647,17 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-gaspar</t>
+          <t>deh-nicolau-pimenta</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Manuel Gaspar</t>
+          <t>Nicolau Pimenta</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Procurador da China e do Japão</t>
+          <t>Visitador das Índias Orientais</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1679,22 +1679,22 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-fernandes</t>
+          <t>deh-manuel-gaspar</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sebastião Fernandes</t>
+          <t>Manuel Gaspar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Destinado à China</t>
+          <t>Procurador da China e do Japão</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1711,27 +1711,27 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-sebastiao-fernandes</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>Sebastião Fernandes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mestre dos Noviços</t>
+          <t>Destinado à China</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1743,22 +1743,22 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Carta anual do Japão</t>
+          <t>Mestre dos Noviços</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1839,27 +1839,27 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-ferreira</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gaspar Ferreira</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mestre dos Noviços</t>
+          <t>Carta anual do Japão</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1871,17 +1871,17 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-gaspar-ferreira</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>Gaspar Ferreira</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Reitor do Colégio de Macau</t>
+          <t>Mestre dos Noviços</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1903,17 +1903,17 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>deh-nicolau-pimenta</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nicolau Pimenta</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Visitador das Índias Orientais</t>
+          <t>Reitor do Colégio de Macau</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1935,22 +1935,22 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-francisco-vieira</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Francisco Vieira</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Carta anual do Japão</t>
+          <t>Provincial de Goa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1999,27 +1999,27 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-nicolau-pimenta</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Nicolau Pimenta</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Carta anual do Japão</t>
+          <t>Visitador das Índias Orientais</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2031,27 +2031,27 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Reitor do Colégio de Macau</t>
+          <t>Carta anual do Japão</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2063,27 +2063,27 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>deh-nicolau-pimenta</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nicolau Pimenta</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Visitador das Índias Orientais</t>
+          <t>Carta anual do Japão</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2095,17 +2095,17 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Visitador das missões</t>
+          <t>Reitor do Colégio de Macau</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2127,17 +2127,17 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-nicolau-pimenta</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>Nicolau Pimenta</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Visitador das missões</t>
+          <t>Visitador das Índias Orientais</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2159,27 +2159,27 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Carta anual da China</t>
+          <t>Visitador das missões</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2191,17 +2191,17 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-francisco-vieira</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>Francisco Vieira</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Provincial do Japão e da China</t>
+          <t>Provincial de Goa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2223,17 +2223,17 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Visitador das províncias do Malabar</t>
+          <t>Visitador das missões</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2255,17 +2255,17 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-francisco-vieira</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>Francisco Vieira</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Secretário da Congregação Provincial do Japão</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Carta anual da Cochichina de 1619</t>
+          <t>Carta anual da China</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2319,17 +2319,17 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Visitador das províncias do Malabar</t>
+          <t>Provincial do Japão e da China</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Visitador das províncias de Goa e do Malabar</t>
+          <t>Visitador das províncias do Malabar</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2383,17 +2383,17 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Secretário da Congregação Provincial do Japão</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2415,27 +2415,27 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Provincial do Japão e da China</t>
+          <t>Carta anual da Cochichina de 1619</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2447,17 +2447,17 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-da-rocha</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>João da Rocha</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Superior da missão da China</t>
+          <t>Visitador das províncias do Malabar</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2479,17 +2479,17 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Visitador das províncias de Goa e do Malabar</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2511,17 +2511,17 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Superior da missão da China</t>
+          <t>Provincial do Japão e da China</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2543,27 +2543,27 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Faz mais de 40000 baptismos no Tonquim</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2575,27 +2575,27 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-joao-da-rocha</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>João da Rocha</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Carta anual da Cochichina de 1622</t>
+          <t>Superior da missão da China</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2607,17 +2607,17 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Procurador da província</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2639,27 +2639,27 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Carta anual do Japão</t>
+          <t>Superior da missão da China</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2671,27 +2671,27 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-andrade</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>António de Andrade</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Visitador de Agra</t>
+          <t>Faz mais de 40000 baptismos no Tonquim</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2703,27 +2703,27 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-andrade</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>António de Andrade</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Superior de Agra</t>
+          <t>Carta anual da Cochichina de 1622</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2735,17 +2735,17 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Procurador da província</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2767,27 +2767,27 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Visitador das províncias de Goa e do Malabar</t>
+          <t>Carta anual do Japão</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2799,17 +2799,17 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-antonio-de-andrade</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>António de Andrade</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Visitador de Agra</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2831,17 +2831,17 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-antonio-de-andrade</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>António de Andrade</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Provincial do Japão e da China</t>
+          <t>Superior de Agra</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2863,27 +2863,27 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Carta anual do Japão</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2895,27 +2895,27 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Preside a conferência de Kiating e mostra-se adversário do emprego de T'ien e Chang-ti para designar Deus</t>
+          <t>Provincial do Japão e da China</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2927,27 +2927,27 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Superior da missão do Tonquim</t>
+          <t>Carta anual do Japão</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2959,17 +2959,17 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-andrade</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>António de Andrade</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Provincial de Goa</t>
+          <t>Visitador das províncias de Goa e do Malabar</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2991,17 +2991,17 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Provincial do Japão e da China</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3023,27 +3023,27 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Preside a conferência de Kiating e mostra-se adversário do emprego de T'ien e Chang-ti para designar Deus</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3055,17 +3055,17 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-andrade</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>António de Andrade</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Provincial de Goa</t>
+          <t>Superior da missão do Tonquim</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Provincial de Goa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3119,17 +3119,17 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Provincial do Japão e da China</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3151,17 +3151,17 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3183,17 +3183,17 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-furtado</t>
+          <t>deh-antonio-de-andrade</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Francisco Furtado</t>
+          <t>António de Andrade</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Vice-provincial da China do Norte</t>
+          <t>Provincial de Goa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3215,12 +3215,12 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-antonio-de-andrade</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>António de Andrade</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3247,27 +3247,27 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>deh-gabriel-de-magalhaes</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Gabriel de Magalhães</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ensinar Filosofia</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3279,27 +3279,27 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-francisco-furtado</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>Francisco Furtado</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Participa numa consulta sobre a China</t>
+          <t>Vice-provincial da China do Norte</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3311,17 +3311,17 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-furtado</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Francisco Furtado</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Vice-provincial da China do Norte</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3343,17 +3343,17 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-furtado</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Francisco Furtado</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Superior das seis residências do Norte</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3375,27 +3375,27 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-gabriel-de-magalhaes</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>Gabriel de Magalhães</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Ensinar Filosofia</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3407,27 +3407,27 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>deh-goncalo-da-fonseca</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Gonçalo da Fonseca</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Procurador da Vice-província da China</t>
+          <t>Participa numa consulta sobre a China</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3439,17 +3439,17 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-francisco-furtado</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>Francisco Furtado</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Vice-provincial da China do Norte</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3471,17 +3471,17 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-da-maia</t>
+          <t>deh-francisco-furtado</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sebastião da Maia</t>
+          <t>Francisco Furtado</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Superior das seis residências do Norte</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3503,17 +3503,17 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-furtado</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Francisco Furtado</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Vice-provincial da China do Sul</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3535,17 +3535,17 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>deh-simao-da-cunha</t>
+          <t>deh-goncalo-da-fonseca</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Simão da Cunha</t>
+          <t>Gonçalo da Fonseca</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Superior das residências de Kienning fou etc</t>
+          <t>Procurador da Vice-província da China</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3567,17 +3567,17 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>deh-simao-da-cunha</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Simão da Cunha</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Procurador da Vice-província da China</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3631,17 +3631,17 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-francisco-furtado</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>Francisco Furtado</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Vice-provincial da China do Sul</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3663,17 +3663,17 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-furtado</t>
+          <t>deh-simao-da-cunha</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Francisco Furtado</t>
+          <t>Simão da Cunha</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Superior das seis residências do Norte</t>
+          <t>Superior das residências de Kienning fou etc</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3695,17 +3695,17 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-da-maia</t>
+          <t>deh-simao-da-cunha</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sebastião da Maia</t>
+          <t>Simão da Cunha</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Procurador da Vice-província da China</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3727,17 +3727,17 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>deh-matias-da-maia</t>
+          <t>deh-sebastiao-da-maia</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Matias da Maia</t>
+          <t>Sebastião da Maia</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Vice-reitor do Colégio de Macau</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3759,17 +3759,17 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-francisco-furtado</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>Francisco Furtado</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Superior das seis residências do Norte</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3791,27 +3791,27 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-jorge</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manuel Jorge</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Escreve a carta anual de 1652-1654</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3823,27 +3823,27 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>deh-gabriel-de-magalhaes</t>
+          <t>deh-sebastiao-da-maia</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Gabriel de Magalhães</t>
+          <t>Sebastião da Maia</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Funda a igreja de Tong-t'ang</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3855,27 +3855,27 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-ferrao</t>
+          <t>deh-matias-da-maia</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>André Ferrão</t>
+          <t>Matias da Maia</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Assina a carta anual da vice-província da China de 1656</t>
+          <t>Vice-reitor do Colégio de Macau</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3887,27 +3887,27 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>deh-matias-da-maia</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Matias da Maia</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Assina a carta anual de Hainan</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3919,27 +3919,27 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>deh-goncalo-da-fonseca</t>
+          <t>deh-manuel-jorge</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Gonçalo da Fonseca</t>
+          <t>Manuel Jorge</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Procurador da Vice-província da China</t>
+          <t>Escreve a carta anual de 1652-1654</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3951,27 +3951,27 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>deh-simao-da-cunha</t>
+          <t>deh-gabriel-de-magalhaes</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Simão da Cunha</t>
+          <t>Gabriel de Magalhães</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Funda a igreja de Tong-t'ang</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3983,27 +3983,27 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>deh-matias-da-maia</t>
+          <t>deh-andre-ferrao</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Matias da Maia</t>
+          <t>André Ferrão</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Assina a carta anual da vice-província da China de 1656</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4015,27 +4015,27 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-da-maia</t>
+          <t>deh-matias-da-maia</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sebastião da Maia</t>
+          <t>Matias da Maia</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Assina a carta anual de Hainan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Procurador da Vice-província da China</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4079,17 +4079,17 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>deh-simao-da-cunha</t>
+          <t>deh-goncalo-da-fonseca</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Simão da Cunha</t>
+          <t>Gonçalo da Fonseca</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Procurador da Vice-província da China</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Procurador da Vice-província da China</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4143,17 +4143,17 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>deh-goncalo-da-fonseca</t>
+          <t>deh-matias-da-maia</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Gonçalo da Fonseca</t>
+          <t>Matias da Maia</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Procurador da Vice-província da China</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4175,27 +4175,27 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-jorge</t>
+          <t>deh-sebastiao-da-maia</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Manuel Jorge</t>
+          <t>Sebastião da Maia</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Constrói a igreja de Nanquim</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4217,17 +4217,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atribui o Kwangtung e o Kwangsi à província do Japão</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4271,17 +4271,17 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>deh-matias-da-maia</t>
+          <t>deh-goncalo-da-fonseca</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Matias da Maia</t>
+          <t>Gonçalo da Fonseca</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Procurador da Vice-província da China</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4303,27 +4303,27 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>deh-matias-da-maia</t>
+          <t>deh-simao-da-cunha</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Matias da Maia</t>
+          <t>Simão da Cunha</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Atribui o Kwangtung e o Kwangsi à província do Japão</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4335,27 +4335,27 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>deh-matias-da-maia</t>
+          <t>deh-manuel-jorge</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Matias da Maia</t>
+          <t>Manuel Jorge</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Constrói a igreja de Nanquim</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4367,17 +4367,17 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>deh-matias-da-maia</t>
+          <t>deh-simao-da-cunha</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Matias da Maia</t>
+          <t>Simão da Cunha</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Reitor do Colégio de Macau</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4399,17 +4399,17 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-gouvea</t>
+          <t>deh-matias-da-maia</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>António de Gouveia</t>
+          <t>Matias da Maia</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Visitador</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4441,17 +4441,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Escreve a carta anual do Japão e da China</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Visitador</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4495,12 +4495,12 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-gouvea</t>
+          <t>deh-matias-da-maia</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>António de Gouveia</t>
+          <t>Matias da Maia</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4527,17 +4527,17 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>deh-tome-pereira</t>
+          <t>deh-matias-da-maia</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tomé (Sancho) Pereira</t>
+          <t>Matias da Maia</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Vice-visitador do Japão e da China</t>
+          <t>Reitor do Colégio de Macau</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4559,27 +4559,27 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>deh-tome-pereira</t>
+          <t>deh-matias-da-maia</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Tomé (Sancho) Pereira</t>
+          <t>Matias da Maia</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Escreve a carta anual do Japão e da China</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4591,17 +4591,17 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>deh-miguel-do-amaral</t>
+          <t>deh-antonio-de-gouvea</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Miguel do Amaral</t>
+          <t>António de Gouveia</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Procurador da Vice-província da China</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4623,27 +4623,27 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-de-sa</t>
+          <t>deh-antonio-de-gouvea</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Manuel de Sá</t>
+          <t>António de Gouveia</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Enviado ao rei</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4655,17 +4655,17 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-de-sa</t>
+          <t>deh-tome-pereira</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Manuel de Sá</t>
+          <t>Tomé (Sancho) Pereira</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Socius de Francesco Maria Spinola</t>
+          <t>Vice-visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Vice-visitador do Japão e da China</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -4719,27 +4719,27 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>deh-tome-pereira</t>
+          <t>deh-manuel-de-sa</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tomé (Sancho) Pereira</t>
+          <t>Manuel de Sá</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Enviado ao rei</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -4751,17 +4751,17 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-da-silva</t>
+          <t>deh-miguel-do-amaral</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>António da Silva</t>
+          <t>Miguel do Amaral</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Reitor de Nanquim</t>
+          <t>Procurador da Vice-província da China</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4783,17 +4783,17 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>deh-leonardo-teixeira</t>
+          <t>deh-manuel-de-sa</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Leonardo Teixeira</t>
+          <t>Manuel de Sá</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Superior</t>
+          <t>Socius de Francesco Maria Spinola</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4815,17 +4815,17 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-da-silva</t>
+          <t>deh-tome-pereira</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>António da Silva</t>
+          <t>Tomé (Sancho) Pereira</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Socius do bispo de Nanquim</t>
+          <t>Vice-visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4847,17 +4847,17 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>deh-miguel-do-amaral</t>
+          <t>deh-tome-pereira</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Miguel do Amaral</t>
+          <t>Tomé (Sancho) Pereira</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4879,17 +4879,17 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-osorio-i</t>
+          <t>deh-antonio-da-silva</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Manuel Osório</t>
+          <t>António da Silva</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Reitor do colégio de Macau</t>
+          <t>Reitor de Nanquim</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4911,17 +4911,17 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-osorio-i</t>
+          <t>deh-leonardo-teixeira</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Manuel Osório</t>
+          <t>Leonardo Teixeira</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Superior</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -4943,17 +4943,17 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>deh-miguel-do-amaral</t>
+          <t>deh-antonio-da-silva</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Miguel do Amaral</t>
+          <t>António da Silva</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Socius do bispo de Nanquim</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -4975,27 +4975,27 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>deh-leonardo-teixeira</t>
+          <t>deh-miguel-do-amaral</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Leonardo Teixeira</t>
+          <t>Miguel do Amaral</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sai da Companhia</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Visitador da província de Goa</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Reitor do colégio de Macau</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Procurador da Província do Japão em Macau</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5103,27 +5103,27 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pinto-i</t>
+          <t>deh-leonardo-teixeira</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Francisco Pinto</t>
+          <t>Leonardo Teixeira</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Sai da Companhia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5167,27 +5167,27 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>deh-tome-pereira</t>
+          <t>deh-manuel-osorio-i</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Tomé (Sancho) Pereira</t>
+          <t>Manuel Osório</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Reconstrói o Nan-t'ang</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5199,17 +5199,17 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>deh-miguel-do-amaral</t>
+          <t>deh-manuel-osorio-i</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Miguel do Amaral</t>
+          <t>Manuel Osório</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Visitador da província de Goa</t>
+          <t>Procurador da Província do Japão em Macau</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Visitador da província de Goa</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5295,27 +5295,27 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-da-silva</t>
+          <t>deh-tome-pereira</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>António da Silva</t>
+          <t>Tomé (Sancho) Pereira</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Reconstrói o Nan-t'ang</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5327,17 +5327,17 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-mendes</t>
+          <t>deh-miguel-do-amaral</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Manuel Mendes</t>
+          <t>Miguel do Amaral</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Visitador da província de Goa</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5359,17 +5359,17 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-da-silva</t>
+          <t>deh-miguel-do-amaral</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>António da Silva</t>
+          <t>Miguel do Amaral</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5391,17 +5391,17 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>deh-estanislau-machado</t>
+          <t>deh-francisco-pinto-i</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Estanislau Machado</t>
+          <t>Francisco Pinto</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Superior da missão do Tonquim</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5423,17 +5423,17 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>deh-estanislau-machado</t>
+          <t>deh-antonio-da-silva</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Estanislau Machado</t>
+          <t>António da Silva</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5455,17 +5455,17 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pinto-i</t>
+          <t>deh-antonio-da-silva</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Francisco Pinto</t>
+          <t>António da Silva</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Procurador do Japão</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5487,17 +5487,17 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>deh-estanislau-machado</t>
+          <t>deh-manuel-mendes</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Estanislau Machado</t>
+          <t>Manuel Mendes</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Superior da missão do Tonquim</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Superior da missão do Tonquim</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5551,12 +5551,12 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>deh-miguel-do-amaral</t>
+          <t>deh-estanislau-machado</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Miguel do Amaral</t>
+          <t>Estanislau Machado</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5583,17 +5583,17 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>deh-miguel-do-amaral</t>
+          <t>deh-francisco-pinto-i</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Miguel do Amaral</t>
+          <t>Francisco Pinto</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Procurador do Japão</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -5647,17 +5647,17 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pinto-i</t>
+          <t>deh-estanislau-machado</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Francisco Pinto</t>
+          <t>Estanislau Machado</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Superior da missão do Tonquim</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -5679,17 +5679,17 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pinto-i</t>
+          <t>deh-estanislau-machado</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Francisco Pinto</t>
+          <t>Estanislau Machado</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Vice-visitador do Japão</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -5711,17 +5711,17 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-mendes</t>
+          <t>deh-miguel-do-amaral</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Manuel Mendes</t>
+          <t>Miguel do Amaral</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -5743,12 +5743,12 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pinto-i</t>
+          <t>deh-miguel-do-amaral</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Francisco Pinto</t>
+          <t>Miguel do Amaral</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Vice-visitador do Japão</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -5807,17 +5807,17 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>deh-miguel-do-amaral</t>
+          <t>deh-francisco-pinto-i</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Miguel do Amaral</t>
+          <t>Francisco Pinto</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Procurador da Vice-província da China</t>
+          <t>Vice-visitador do Japão</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -5839,27 +5839,27 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-melo</t>
+          <t>deh-miguel-do-amaral</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>António de Melo</t>
+          <t>Miguel do Amaral</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Presta Juramento</t>
+          <t>Procurador da Vice-província da China</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -5871,12 +5871,12 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-gomes</t>
+          <t>deh-manuel-mendes</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>António Gomes</t>
+          <t>Manuel Mendes</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -5903,17 +5903,17 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-montanha-ii</t>
+          <t>deh-francisco-pinto-i</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>José Montanha</t>
+          <t>Francisco Pinto</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -5935,17 +5935,17 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-gomes</t>
+          <t>deh-francisco-pinto-i</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>António Gomes</t>
+          <t>Francisco Pinto</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Vice-visitador do Japão</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -5967,27 +5967,27 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-montanha-ii</t>
+          <t>deh-antonio-de-melo</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>José Montanha</t>
+          <t>António de Melo</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Presta Juramento</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -5999,30 +5999,158 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
+          <t>deh-antonio-gomes</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>António Gomes</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Vice-provincial da China</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>jesuita-cargo</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>1748</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
           <t>deh-jose-montanha-ii</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>José Montanha</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Provincial do Japão</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>jesuita-cargo</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>deh-antonio-gomes</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>António Gomes</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Vice-provincial da China</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>jesuita-cargo</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>deh-jose-montanha-ii</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>José Montanha</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Provincial do Japão</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>jesuita-cargo</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1752</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>deh-jose-montanha-ii</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>José Montanha</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
         <is>
           <t>Procurador</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>jesuita-cargo</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>jesuita-cargo</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
         <is>
           <t>1753</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>n</t>
         </is>
